--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
+          <t>R$ 208,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,5%</t>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,22 +738,22 @@
           <t>R$ 417,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,9%</t>
+        <v>63</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,8%</t>
+          <t>R$ 625,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>76</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 31,6%</t>
+          <t>R$ 486,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>54</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,7%</t>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 555,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 225,0%</t>
+        <v>82</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1401,24 +1401,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▲ 180,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>81</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>96</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,59 +1684,55 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1761,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>65</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1843,24 +1839,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2053,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2062,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2126,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2134,8 +2130,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>7</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2144,37 +2142,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2242,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2356,7 +2356,7 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2426,51 +2426,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,33 +2491,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,8%</t>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2538,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2568,7 +2564,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2576,10 +2572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2588,39 +2582,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,33 +2637,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 73,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2761,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2791,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2911,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2941,33 +2933,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+        <v>49</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2976,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3014,7 +3006,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3022,8 +3014,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3032,37 +3026,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3090,22 +3086,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,9%</t>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3113,7 +3109,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3163,9 +3159,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -3203,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3233,33 +3229,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>46</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3276,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3306,16 +3302,18 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3324,37 +3322,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3379,33 +3379,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 83,4%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>50</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3463,9 +3463,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3474,11 +3474,11 @@
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3525,33 +3525,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>51</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3601,17 +3601,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3671,33 +3671,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,5%</t>
+        <v>113</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3744,33 +3744,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3817,33 +3817,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
+          <t>R$ 1.313,00</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3890,33 +3890,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3963,33 +3963,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,8%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4036,33 +4036,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4109,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,6%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,5%</t>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t>6,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4191,24 +4191,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4255,33 +4255,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
+          <t>R$ 836,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▲ 112,3%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>252</v>
+        <v>176</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,1%</t>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4331,17 +4331,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4401,33 +4401,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
+          <t>R$ 1.194,00</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4474,33 +4474,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4547,38 +4547,38 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 836,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,0%</t>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,4%</t>
+        <v>233</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4629,24 +4629,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4693,33 +4693,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,3%</t>
+          <t>R$ 1.015,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4769,17 +4769,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4839,33 +4839,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,1%</t>
+          <t>R$ 478,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>219</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4912,33 +4912,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>20</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4985,38 +4985,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>▼ 56,5%</t>
+          <t>▲ 9,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,0%</t>
+          <t>▼ 10,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5028,12 +5028,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5067,11 +5067,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5080,11 +5080,11 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,38 +5131,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,8%</t>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,3%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+        <v>183</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5213,11 +5213,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,38 +5277,38 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
+          <t>R$ 537,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 10,1%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,5%</t>
+        <v>198</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5353,17 +5353,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▼ 56,5%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,6%</t>
+        <v>193</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5505,24 +5505,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,38 +5569,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 1.373,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 27,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>182</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5651,11 +5651,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5718,35 +5718,35 @@
           <t>R$ 1.074,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 63,5%</t>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,5%</t>
+        <v>188</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5791,17 +5791,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 9,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5943,24 +5943,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6007,33 +6007,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>146</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6089,11 +6089,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6120,8 +6120,446 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 139,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,1%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -662,25 +662,25 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
+          <t>R$ 208,00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>64</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 625,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,7%</t>
+        <v>63</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
+          <t>R$ 625,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>76</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 486,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,9%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,8%</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>78</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 555,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>82</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 225,0%</t>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1835,20 +1835,20 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 180,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>65</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2067,15 +2067,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2130,10 +2130,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2142,39 +2140,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2242,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2272,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,8 +2276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2290,39 +2288,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2348,17 +2348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2429,9 +2429,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2491,33 +2491,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,14 +2534,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2646,24 +2646,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2753,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2786,17 +2786,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,10 +2864,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2876,41 +2874,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2933,33 +2929,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2976,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3053,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3083,33 +3079,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,9%</t>
+        <v>49</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3156,7 +3152,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3164,8 +3160,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3174,39 +3172,41 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3229,33 +3229,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>80</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3310,10 +3310,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3322,41 +3320,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3379,7 +3375,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3388,24 +3384,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3422,14 +3418,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3452,7 +3448,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3460,8 +3456,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3470,39 +3468,41 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3525,33 +3525,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,9%</t>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3568,14 +3568,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3601,9 +3601,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
@@ -3641,14 +3641,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3671,33 +3671,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,0%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,14 +3714,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3766,11 +3766,11 @@
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3787,14 +3787,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3817,16 +3817,16 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,4%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3835,15 +3835,15 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3860,14 +3860,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3890,20 +3890,20 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,4%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3933,14 +3933,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3963,20 +3963,20 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 1.313,00</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3985,11 +3985,11 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4006,14 +4006,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4036,33 +4036,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4079,14 +4079,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4109,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,14 +4152,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4182,33 +4182,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4225,14 +4225,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4255,33 +4255,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,1%</t>
+        <v>184</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4298,14 +4298,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4328,33 +4328,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 62,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4371,14 +4371,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4401,33 +4401,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,8%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4444,14 +4444,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4474,33 +4474,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>16</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4517,14 +4517,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4547,33 +4547,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,6%</t>
+          <t>R$ 1.194,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,14 +4590,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4629,24 +4629,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>14</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4663,14 +4663,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4693,33 +4693,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,3%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,1%</t>
+        <v>233</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,14 +4736,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4769,17 +4769,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,0%</t>
+        <v>22</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4809,14 +4809,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4839,33 +4839,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 1.015,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,14 +4882,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4912,33 +4912,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,14 +4955,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4985,38 +4985,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,0%</t>
+          <t>R$ 478,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,4%</t>
+        <v>219</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
           <t>7,3%</t>
         </is>
       </c>
-      <c r="L62" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5028,14 +5028,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5063,20 +5063,20 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,14 +5101,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5131,38 +5131,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,3%</t>
+          <t>▲ 9,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▼ 10,4%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5174,14 +5174,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5213,11 +5213,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5226,11 +5226,11 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,14 +5247,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5277,33 +5277,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,1%</t>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,3%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>183</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5320,14 +5320,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5359,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,14 +5393,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5423,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 537,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,5%</t>
+          <t>▼ 10,1%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,0%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,14 +5466,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5505,11 +5505,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5539,14 +5539,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5569,38 +5569,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,8%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 56,5%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+        <v>193</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5612,14 +5612,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5651,11 +5651,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5685,14 +5685,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5715,33 +5715,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
+          <t>R$ 1.373,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 27,8%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,5%</t>
+        <v>182</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5758,14 +5758,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5791,17 +5791,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,14 +5831,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5861,38 +5861,38 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 1.074,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,6%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -5904,14 +5904,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5934,33 +5934,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>4</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5977,14 +5977,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6007,33 +6007,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>160</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,6%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,14 +6050,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6089,24 +6089,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6123,14 +6123,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6153,33 +6153,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,5%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,5%</t>
+        <v>146</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6196,14 +6196,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6235,11 +6235,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6269,14 +6269,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6299,33 +6299,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>179</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6342,14 +6342,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6381,11 +6381,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6415,14 +6415,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6450,20 +6450,20 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>151</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6558,8 +6558,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 367,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▲ 66,8%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 220,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>28</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 147,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 101,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 625,00</t>
+          <t>R$ 139,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,7%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,25 +1100,25 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
+          <t>R$ 208,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,5%</t>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,22 +1322,22 @@
           <t>R$ 417,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,9%</t>
+        <v>63</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,8%</t>
+          <t>R$ 625,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>76</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 31,6%</t>
+          <t>R$ 486,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>54</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 47,7%</t>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 555,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 225,0%</t>
+        <v>82</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 180,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>81</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>96</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,59 +2268,55 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>65</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2418,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2427,24 +2423,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2461,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2573,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2637,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2646,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2710,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2718,8 +2714,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>7</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2728,37 +2726,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2826,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2899,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2940,7 +2940,7 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2972,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3010,51 +3010,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,33 +3075,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,8%</t>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,7 +3148,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3160,10 +3156,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3172,39 +3166,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3229,33 +3221,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3345,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3375,33 +3367,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3418,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3495,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3525,33 +3517,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+        <v>49</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3568,12 +3560,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3598,7 +3590,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3606,8 +3598,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3616,37 +3610,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3674,22 +3670,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,9%</t>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3697,7 +3693,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3747,9 +3743,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3787,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3817,33 +3813,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>46</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3860,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3890,16 +3886,18 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3908,37 +3906,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3963,33 +3963,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,4%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>50</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4047,9 +4047,9 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4058,11 +4058,11 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4109,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>51</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4185,17 +4185,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4255,33 +4255,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,5%</t>
+        <v>113</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4328,33 +4328,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,4%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4401,33 +4401,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
+          <t>R$ 1.313,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4474,33 +4474,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4547,33 +4547,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,8%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4620,33 +4620,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4693,33 +4693,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,6%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,5%</t>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
           <t>6,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4775,24 +4775,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4839,33 +4839,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
+          <t>R$ 836,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▲ 112,3%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>252</v>
+        <v>176</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,1%</t>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4985,33 +4985,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
+          <t>R$ 1.194,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5028,12 +5028,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5058,33 +5058,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,38 +5131,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 836,00</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,0%</t>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,4%</t>
+        <v>233</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5213,24 +5213,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,33 +5277,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,3%</t>
+          <t>R$ 1.015,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5353,17 +5353,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,1%</t>
+          <t>R$ 478,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>219</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5496,33 +5496,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>20</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,38 +5569,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,5%</t>
+          <t>▲ 9,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,0%</t>
+          <t>▼ 10,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5651,11 +5651,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5664,11 +5664,11 @@
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5715,38 +5715,38 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,8%</t>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+        <v>183</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5797,11 +5797,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5861,38 +5861,38 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
+          <t>R$ 537,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 10,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,5%</t>
+        <v>198</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6007,33 +6007,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▼ 56,5%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,6%</t>
+        <v>193</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6089,24 +6089,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6153,38 +6153,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 1.373,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 27,8%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>182</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6235,11 +6235,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6302,35 +6302,35 @@
           <t>R$ 1.074,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,5%</t>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,5%</t>
+        <v>188</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6375,17 +6375,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6445,25 +6445,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 9,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6527,24 +6527,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6591,33 +6591,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>146</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6704,8 +6704,446 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>88</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 367,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,8%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,9%</t>
+          <t>▼ 45,5%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 220,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,7%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▲ 86,7%</t>
+          <t>▲ 106,2%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 720,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 147,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 101,4%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,6%</t>
+          <t>R$ 367,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 17,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 220,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▲ 86,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 147,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 101,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 625,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,7%</t>
+        <v>52</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,25 +1538,25 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,5%</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>64</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,16 +1693,16 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1762,20 +1762,20 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,9%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
+          <t>R$ 625,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▲ 166,8%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 486,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 417,00</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 47,7%</t>
+        <v>78</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 555,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 225,0%</t>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2423,24 +2423,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 180,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>81</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2563,17 +2563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>96</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,59 +2706,55 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2783,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>65</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2865,24 +2861,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2899,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2929,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3011,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3075,7 +3071,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3084,24 +3080,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3148,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3156,8 +3152,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>7</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3166,37 +3164,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3264,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3448,51 +3448,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3517,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 38,8%</t>
+        <v>29</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3590,7 +3586,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3598,10 +3594,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3610,39 +3604,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3667,33 +3659,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 73,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3710,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3783,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3813,33 +3805,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3933,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3963,33 +3955,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4006,12 +3998,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4036,7 +4028,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4044,8 +4036,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4054,37 +4048,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4114,20 +4110,20 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,9%</t>
+        <v>80</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4135,7 +4131,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4185,9 +4181,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
@@ -4225,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4255,33 +4251,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>46</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4298,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4328,16 +4324,18 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4346,37 +4344,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4401,33 +4401,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>50</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4485,9 +4485,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4496,11 +4496,11 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4547,33 +4547,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4629,11 +4629,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4693,33 +4693,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,5%</t>
+        <v>113</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4766,33 +4766,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,4%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4839,33 +4839,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+          <t>R$ 1.313,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4912,33 +4912,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4985,33 +4985,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,8%</t>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5028,12 +5028,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5058,33 +5058,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>20</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,33 +5131,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+        <v>184</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
           <t>6,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5213,24 +5213,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,8%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,33 +5277,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 112,3%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,1%</t>
+        <v>176</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5359,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 1.194,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>219</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,5%</t>
+        <v>178</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5496,33 +5496,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,38 +5569,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,0%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,4%</t>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5651,24 +5651,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5715,33 +5715,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
+          <t>R$ 1.015,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,3%</t>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,6%</t>
+        <v>252</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5791,17 +5791,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 5,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5861,33 +5861,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
+          <t>R$ 478,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,1%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5934,33 +5934,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>20</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6007,38 +6007,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 56,5%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,0%</t>
+        <v>164</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6089,11 +6089,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6102,11 +6102,11 @@
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6153,38 +6153,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
+          <t>R$ 657,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,8%</t>
+          <t>▲ 22,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,2%</t>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6235,11 +6235,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6299,38 +6299,38 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 537,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,1%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,5%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6375,17 +6375,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6445,33 +6445,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,5%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,6%</t>
+          <t>▲ 6,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6527,24 +6527,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6591,38 +6591,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>R$ 1.373,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,8%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,4%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6742,33 +6742,33 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▲ 63,5%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,5%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6813,17 +6813,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6883,25 +6883,25 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>160</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,6%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6965,24 +6965,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6999,12 +6999,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7029,33 +7029,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>146</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7111,11 +7111,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7142,8 +7142,446 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 45,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,1%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 106,2%</t>
+        <v>18</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 45,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 720,0%</t>
+          <t>▲ 17,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -957,22 +957,22 @@
           <t>R$ 73,00</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,1%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>33</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 106,2%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1032,20 +1032,20 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>41</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 720,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 367,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,8%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,9%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1191,15 +1191,15 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 220,00</t>
+          <t>R$ 367,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,7%</t>
+          <t>▲ 66,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 86,7%</t>
+        <v>23</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,9%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 147,00</t>
+          <t>R$ 220,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▲ 101,4%</t>
+          <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▲ 86,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,6%</t>
+          <t>R$ 147,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 101,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>15</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 139,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,1%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1684,25 +1684,25 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
+          <t>R$ 208,00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>64</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 625,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,7%</t>
+        <v>63</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
+          <t>R$ 625,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>76</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2127,20 +2127,20 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 486,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,9%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2277,24 +2277,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,8%</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>78</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2423,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 555,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>82</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2563,17 +2563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 47,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 225,0%</t>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2857,20 +2857,20 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 180,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>65</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3007,24 +3007,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3089,15 +3089,15 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3152,10 +3152,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3164,39 +3162,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3264,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3294,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3302,8 +3298,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3312,39 +3310,41 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3370,17 +3370,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3451,9 +3451,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3513,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3668,24 +3668,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3808,17 +3808,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3886,10 +3886,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3898,41 +3896,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -3955,33 +3951,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3998,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4075,14 +4071,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4105,33 +4101,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 73,9%</t>
+        <v>49</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4148,14 +4144,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4178,7 +4174,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4186,8 +4182,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4196,39 +4194,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4251,33 +4251,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>80</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4294,14 +4294,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4332,10 +4332,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4344,41 +4342,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4401,7 +4397,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -4410,24 +4406,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4444,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4474,7 +4470,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4482,8 +4478,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4492,39 +4490,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4547,33 +4547,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,9%</t>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,14 +4590,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4623,9 +4623,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
@@ -4663,14 +4663,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4693,33 +4693,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,0%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,14 +4736,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -4788,11 +4788,11 @@
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4809,14 +4809,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4839,16 +4839,16 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 83,4%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4857,15 +4857,15 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,14 +4882,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4912,20 +4912,20 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,4%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,14 +4955,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 1.313,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5007,11 +5007,11 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5028,14 +5028,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5058,33 +5058,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,14 +5101,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5131,33 +5131,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,14 +5174,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5204,33 +5204,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,14 +5247,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5277,33 +5277,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,1%</t>
+        <v>184</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5320,14 +5320,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5350,33 +5350,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 62,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5393,14 +5393,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5423,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,8%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,14 +5466,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5496,33 +5496,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>16</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5539,14 +5539,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5569,33 +5569,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,6%</t>
+          <t>R$ 1.194,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5612,14 +5612,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5651,24 +5651,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>14</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5685,14 +5685,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5715,33 +5715,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 112,3%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,1%</t>
+        <v>233</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5758,14 +5758,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5791,17 +5791,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,0%</t>
+        <v>22</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,14 +5831,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5861,33 +5861,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 1.015,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5904,14 +5904,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -5934,33 +5934,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5977,14 +5977,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6007,38 +6007,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,0%</t>
+          <t>R$ 478,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,4%</t>
+        <v>219</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
           <t>7,3%</t>
         </is>
       </c>
-      <c r="L76" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6050,14 +6050,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6123,14 +6123,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6153,38 +6153,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,3%</t>
+          <t>▲ 9,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▼ 10,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6196,14 +6196,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6235,11 +6235,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6248,11 +6248,11 @@
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6269,14 +6269,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6299,33 +6299,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,1%</t>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,3%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>183</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6342,14 +6342,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6381,11 +6381,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6415,14 +6415,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6445,33 +6445,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 537,00</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>▼ 56,5%</t>
+          <t>▼ 10,1%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,0%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6488,14 +6488,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6527,11 +6527,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6561,14 +6561,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6591,38 +6591,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,8%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,5%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+        <v>193</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6634,14 +6634,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6707,14 +6707,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6737,33 +6737,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
+          <t>R$ 1.373,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 27,8%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,5%</t>
+        <v>182</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6780,14 +6780,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6813,17 +6813,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6853,14 +6853,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6883,38 +6883,38 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 1.074,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,6%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -6926,14 +6926,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -6956,33 +6956,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6999,14 +6999,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7029,33 +7029,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>160</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,6%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7072,14 +7072,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7111,24 +7111,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7145,14 +7145,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7175,33 +7175,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▲ 63,5%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,5%</t>
+        <v>146</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7218,14 +7218,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7257,11 +7257,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7291,14 +7291,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7321,33 +7321,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>179</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7364,14 +7364,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7403,11 +7403,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7437,14 +7437,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-144-PT</t>
@@ -7472,20 +7472,20 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>151</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7580,8 +7580,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 99,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>90</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -665,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 44,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 294,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 45,5%</t>
+        <v>23</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 473,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,1%</t>
+        <v>88</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 106,2%</t>
+        <v>26</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 720,0%</t>
+        <v>88</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,22 +1103,22 @@
           <t>R$ 73,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,1%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>18</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 45,5%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 367,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,8%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,9%</t>
+          <t>▲ 106,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>41</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 720,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 220,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,7%</t>
+          <t>▼ 80,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 86,7%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 147,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 101,4%</t>
+          <t>R$ 367,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 17,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 220,00</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 86,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 147,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 101,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>52</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 625,00</t>
+          <t>R$ 208,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,7%</t>
+        <v>64</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2127,20 +2127,20 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
+          <t>R$ 417,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>63</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
+          <t>R$ 625,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,9%</t>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,8%</t>
+          <t>R$ 486,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 417,00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>78</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 555,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 47,7%</t>
+        <v>82</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,25 +2925,25 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 225,0%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 180,0%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>96</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>65</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3298,51 +3298,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3367,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3376,7 +3372,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3385,15 +3381,15 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3449,7 +3445,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3483,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3516,17 +3512,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3556,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3586,7 +3582,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3594,47 +3590,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3668,24 +3668,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3775,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3808,17 +3808,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3889,9 +3889,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3951,33 +3951,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4032,10 +4032,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4044,39 +4042,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4101,33 +4097,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 38,8%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4174,7 +4170,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4182,10 +4178,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4194,39 +4188,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4251,33 +4243,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4294,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4324,7 +4316,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4332,8 +4324,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4342,37 +4336,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4397,33 +4393,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>49</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4440,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4517,12 +4513,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4547,33 +4543,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,12 +4586,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4663,12 +4659,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4693,33 +4689,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,9%</t>
+        <v>46</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,12 +4732,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4766,16 +4762,18 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4784,37 +4782,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4839,33 +4839,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>50</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
@@ -4934,11 +4934,11 @@
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4985,33 +4985,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,4%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5028,12 +5028,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5058,20 +5058,20 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5080,11 +5080,11 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,33 +5131,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>113</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,20 +5204,20 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 27,4%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5226,11 +5226,11 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,33 +5277,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 1.313,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5359,24 +5359,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5499,17 +5499,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,33 +5569,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,8%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5651,24 +5651,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5718,22 +5718,22 @@
           <t>R$ 836,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,6%</t>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+        <v>176</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5791,17 +5791,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5861,33 +5861,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 112,3%</t>
+          <t>R$ 1.194,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,1%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5934,33 +5934,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6007,33 +6007,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6080,33 +6080,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6153,38 +6153,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,0%</t>
+          <t>R$ 1.015,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,4%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6226,33 +6226,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6299,33 +6299,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
+          <t>R$ 478,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,3%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,6%</t>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6372,33 +6372,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6445,38 +6445,38 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
+          <t>R$ 716,00</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,1%</t>
+          <t>▲ 9,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▼ 10,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6527,11 +6527,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6540,11 +6540,11 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6591,33 +6591,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 657,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▼ 56,5%</t>
+          <t>▲ 22,3%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,0%</t>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6737,38 +6737,38 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
+          <t>R$ 537,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,8%</t>
+          <t>▼ 10,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,2%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6819,11 +6819,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6883,38 +6883,38 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 56,5%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,5%</t>
+        <v>193</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6959,17 +6959,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6999,12 +6999,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7029,38 +7029,38 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+          <t>R$ 1.373,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,8%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,6%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7111,24 +7111,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7175,38 +7175,38 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
+          <t>R$ 1.074,00</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,4%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7251,17 +7251,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7291,12 +7291,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7321,33 +7321,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▲ 63,5%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,5%</t>
+        <v>160</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,6%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7403,24 +7403,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7467,33 +7467,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>146</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7549,11 +7549,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7613,33 +7613,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>179</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7726,8 +7726,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-144-PT-ESCORREDOR-EXTENSIVEL-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 710,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 798,7%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>56</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 105,5%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,4%</t>
+        <v>52</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 294,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,5%</t>
+        <v>61</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,6%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>52</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 294,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 33,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 44,4%</t>
+        <v>63</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,25 +1027,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>66</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,20 +1100,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 220,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 45,5%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1122,11 +1122,11 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,1%</t>
+          <t>▼ 32,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 147,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 106,2%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 720,0%</t>
+        <v>87</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,1%</t>
+          <t>R$ 220,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 367,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,8%</t>
+          <t>R$ 220,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,9%</t>
+          <t>▲ 104,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1687,22 +1687,22 @@
           <t>R$ 220,00</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 86,7%</t>
+          <t>▼ 37,8%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 20,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1835,20 +1835,20 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 101,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 5,1%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 10,1%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,6%</t>
+          <t>R$ 294,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 160,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,1%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,6%</t>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▼ 53,1%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▲ 28,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>32</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 625,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,7%</t>
+        <v>90</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 486,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,5%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>78</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 294,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>23</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,25 +2633,25 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 417,00</t>
+          <t>R$ 473,00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,9%</t>
+        <v>88</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 555,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,8%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>88</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 45,5%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 208,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 17,1%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 106,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,7%</t>
+        <v>41</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 720,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,25 +3144,25 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>16</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 225,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 367,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 180,0%</t>
+          <t>▼ 17,9%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3381,15 +3381,15 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 220,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3512,17 +3512,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,59 +3582,55 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 147,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 101,4%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3659,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>52</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3732,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3775,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3805,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,1%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3848,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3878,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3887,24 +3883,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3921,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3951,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 417,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 2800,0%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3994,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4027,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4097,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 625,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>76</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4140,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4170,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4213,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4243,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 486,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 16,5%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>54</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4286,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4316,59 +4312,55 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4393,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 417,00</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,8%</t>
+        <v>78</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4466,59 +4458,55 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I55" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4543,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 555,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 166,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,9%</t>
+        <v>82</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4586,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4625,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4659,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4689,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 208,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>81</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4732,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4762,59 +4750,55 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4844,20 +4828,20 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▲ 47,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4865,7 +4849,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4912,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4985,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,9%</t>
+          <t>▲ 225,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5028,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5058,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 180,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,16 +5115,16 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5149,15 +5133,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,12 +5261,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.313,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -5299,11 +5283,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5320,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5350,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5358,47 +5342,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,20 +5411,20 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5445,11 +5433,11 @@
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5499,17 +5487,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5539,12 +5527,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,33 +5557,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5612,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5642,7 +5630,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5651,24 +5639,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5685,12 +5673,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5715,33 +5703,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,1%</t>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5758,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5791,17 +5779,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5861,33 +5849,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.194,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,6%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5904,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5934,7 +5922,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5943,24 +5931,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5977,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6007,33 +5995,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 836,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6080,7 +6068,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6088,47 +6076,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6153,33 +6145,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.015,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,3%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,1%</t>
+          <t>▼ 38,8%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6196,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6226,55 +6218,59 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6299,33 +6295,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 478,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>219</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,5%</t>
+        <v>80</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6342,12 +6338,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6372,16 +6368,16 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6390,15 +6386,15 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6415,12 +6411,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6445,38 +6441,38 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,4%</t>
+        <v>46</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6488,12 +6484,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6518,7 +6514,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 62,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6526,47 +6522,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6591,33 +6591,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,3%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,6%</t>
+        <v>50</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6737,33 +6737,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 537,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,1%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>198</v>
+        <v>51</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▼ 54,9%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6813,17 +6813,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6883,33 +6883,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 56,5%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,0%</t>
+        <v>113</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6956,33 +6956,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,4%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6999,12 +6999,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7029,38 +7029,38 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.373,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,8%</t>
+          <t>R$ 1.313,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,4%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7124,11 +7124,11 @@
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7175,38 +7175,38 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7251,17 +7251,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7291,12 +7291,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7321,33 +7321,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 716,00</t>
+          <t>R$ 597,00</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,6%</t>
+        <v>184</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 124,00</t>
+          <t>R$ 62,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7403,24 +7403,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>18</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7467,33 +7467,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 597,00</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>176</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7543,17 +7543,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7613,33 +7613,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.074,00</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,5%</t>
+          <t>R$ 1.194,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,8%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 124,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7695,24 +7695,24 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7759,33 +7759,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 836,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>233</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7841,11 +7841,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>22</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7875,12 +7875,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7905,33 +7905,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 657,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 1.015,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 112,3%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>252</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7981,17 +7981,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8018,8 +8018,1760 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 478,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 62,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,0%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,4%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 62,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,3%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,6%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 537,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,1%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,5%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.373,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,8%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,5%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 716,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,6%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 124,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 597,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.074,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,5%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,5%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4645129694</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 657,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-144-PT</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor extensivel preto</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4468806251</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>